--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484874_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484874_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.057600000000001</v>
+        <v>6.429</v>
       </c>
       <c r="E2" t="n">
-        <v>6.3433</v>
+        <v>4.9792</v>
       </c>
       <c r="F2" t="n">
-        <v>1.7143</v>
+        <v>1.4498</v>
       </c>
       <c r="G2" t="n">
         <v>2.0226</v>
@@ -610,13 +610,13 @@
         <v>3.3966</v>
       </c>
       <c r="S2" t="n">
-        <v>3.1861</v>
+        <v>1.5575</v>
       </c>
       <c r="T2" t="n">
-        <v>2.9785</v>
+        <v>1.6145</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2076</v>
+        <v>-0.057</v>
       </c>
       <c r="V2" t="n">
         <v>2.4714</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.8799</v>
+        <v>6.0722</v>
       </c>
       <c r="E3" t="n">
-        <v>3.7777</v>
+        <v>4.1288</v>
       </c>
       <c r="F3" t="n">
-        <v>2.1022</v>
+        <v>1.9435</v>
       </c>
       <c r="G3" t="n">
         <v>0.5343</v>
@@ -688,13 +688,13 @@
         <v>3.2079</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1758</v>
+        <v>0.3681</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1328</v>
+        <v>0.4839</v>
       </c>
       <c r="U3" t="n">
-        <v>0.043</v>
+        <v>-0.1158</v>
       </c>
       <c r="V3" t="n">
         <v>2.1506</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.2234</v>
+        <v>5.4228</v>
       </c>
       <c r="E4" t="n">
-        <v>4.0199</v>
+        <v>3.9813</v>
       </c>
       <c r="F4" t="n">
-        <v>1.2034</v>
+        <v>1.4415</v>
       </c>
       <c r="G4" t="n">
         <v>3.8367</v>
@@ -766,13 +766,13 @@
         <v>2.2644</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0658</v>
+        <v>0.2653</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4391</v>
+        <v>0.4004</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3733</v>
+        <v>-0.1352</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,10 +799,10 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.0138</v>
+        <v>4.6958</v>
       </c>
       <c r="E5" t="n">
-        <v>3.4795</v>
+        <v>4.1615</v>
       </c>
       <c r="F5" t="n">
         <v>0.5343</v>
@@ -844,10 +844,10 @@
         <v>1.1322</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0958</v>
+        <v>0.5862000000000001</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2939</v>
+        <v>0.3881</v>
       </c>
       <c r="U5" t="n">
         <v>0.1981</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.7126</v>
+        <v>3.9746</v>
       </c>
       <c r="E6" t="n">
-        <v>3.0829</v>
+        <v>3.2391</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6297</v>
+        <v>0.7355</v>
       </c>
       <c r="G6" t="n">
         <v>3.1935</v>
@@ -922,13 +922,13 @@
         <v>0.5661</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.047</v>
+        <v>0.215</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0835</v>
+        <v>0.2397</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1305</v>
+        <v>-0.0247</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>O. CASTRILLON RODRIGUEZ</t>
+          <t>P. LUENGO MATEO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.0894</v>
+        <v>3.1583</v>
       </c>
       <c r="E7" t="n">
-        <v>1.6768</v>
+        <v>2.8714</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4125</v>
+        <v>0.2869</v>
       </c>
       <c r="G7" t="n">
-        <v>2.6989</v>
+        <v>-0.6151</v>
       </c>
       <c r="H7" t="n">
-        <v>2.4065</v>
+        <v>1.2232</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2924</v>
+        <v>-1.8383</v>
       </c>
       <c r="J7" t="n">
-        <v>3.2961</v>
+        <v>1.5017</v>
       </c>
       <c r="K7" t="n">
-        <v>3.74</v>
+        <v>1.5002</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.4439</v>
+        <v>0.0015</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.5972</v>
+        <v>-2.1168</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.3335</v>
+        <v>-0.277</v>
       </c>
       <c r="O7" t="n">
-        <v>0.7363</v>
+        <v>-1.8398</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.9435</v>
+        <v>2.2644</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.887</v>
+        <v>-0.1887</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9435</v>
+        <v>2.4531</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3339</v>
+        <v>0.5846</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0341</v>
+        <v>0.634</v>
       </c>
       <c r="U7" t="n">
-        <v>0.368</v>
+        <v>-0.0493</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.9244</v>
       </c>
       <c r="W7" t="n">
-        <v>0.3018</v>
+        <v>0.9244</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.3018</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. LUENGO MATEO</t>
+          <t>O. CASTRILLON RODRIGUEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.9723</v>
+        <v>2.5946</v>
       </c>
       <c r="E8" t="n">
-        <v>1.897</v>
+        <v>2.2614</v>
       </c>
       <c r="F8" t="n">
-        <v>0.07530000000000001</v>
+        <v>0.3332</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.6151</v>
+        <v>2.6989</v>
       </c>
       <c r="H8" t="n">
-        <v>1.2232</v>
+        <v>2.4065</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.8383</v>
+        <v>0.2924</v>
       </c>
       <c r="J8" t="n">
-        <v>1.5017</v>
+        <v>3.2961</v>
       </c>
       <c r="K8" t="n">
-        <v>1.5002</v>
+        <v>3.74</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0015</v>
+        <v>-0.4439</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.1168</v>
+        <v>-0.5972</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.277</v>
+        <v>-1.3335</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.8398</v>
+        <v>0.7363</v>
       </c>
       <c r="P8" t="n">
-        <v>2.2644</v>
+        <v>-0.9435</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.1887</v>
+        <v>-1.887</v>
       </c>
       <c r="R8" t="n">
-        <v>2.4531</v>
+        <v>0.9435</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6014</v>
+        <v>0.8391999999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3404</v>
+        <v>0.5505</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.261</v>
+        <v>0.2887</v>
       </c>
       <c r="V8" t="n">
-        <v>0.9244</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.9244</v>
+        <v>0.3018</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>1.4261</v>
+        <v>1.4442</v>
       </c>
       <c r="E10" t="n">
-        <v>1.6835</v>
+        <v>1.7809</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2574</v>
+        <v>-0.3367</v>
       </c>
       <c r="G10" t="n">
         <v>2.1533</v>
@@ -1234,13 +1234,13 @@
         <v>0.1887</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0277</v>
+        <v>0.0457</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1176</v>
+        <v>-0.0201</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1452</v>
+        <v>0.0659</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>P. FAYE</t>
+          <t>D. MARTÍNEZ JURADO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9184</v>
+        <v>0.617</v>
       </c>
       <c r="E11" t="n">
-        <v>1.7242</v>
+        <v>0.617</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.8058999999999999</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.6391</v>
+        <v>0.617</v>
       </c>
       <c r="H11" t="n">
-        <v>0.835</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.4742</v>
+        <v>0.617</v>
       </c>
       <c r="J11" t="n">
-        <v>1.0718</v>
+        <v>0.617</v>
       </c>
       <c r="K11" t="n">
-        <v>1.0307</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0411</v>
+        <v>0.617</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.7109</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.1956</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.5153</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.3774</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1322</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.7548</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.2367</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>1.7847</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4521</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.3018</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.3018</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>D. MARTÍNEZ JURADO</t>
+          <t>P. FAYE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>0.617</v>
+        <v>-0.3386</v>
       </c>
       <c r="E12" t="n">
-        <v>0.617</v>
+        <v>0.6525</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>-0.991</v>
       </c>
       <c r="G12" t="n">
-        <v>0.617</v>
+        <v>-0.6391</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>0.835</v>
       </c>
       <c r="I12" t="n">
-        <v>0.617</v>
+        <v>-1.4742</v>
       </c>
       <c r="J12" t="n">
-        <v>0.617</v>
+        <v>1.0718</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>1.0307</v>
       </c>
       <c r="L12" t="n">
-        <v>0.617</v>
+        <v>0.0411</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>-1.7109</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>-0.1956</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>-1.5153</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>-0.3774</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-1.1322</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>0.7548</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>0.9798</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>0.7129</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>0.2669</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>-0.3018</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.6133999999999999</v>
+        <v>-0.3959</v>
       </c>
       <c r="E13" t="n">
-        <v>1.2087</v>
+        <v>1.2675</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.8221</v>
+        <v>-1.6634</v>
       </c>
       <c r="G13" t="n">
         <v>2.0333</v>
@@ -1468,13 +1468,13 @@
         <v>0.9435</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.7789</v>
+        <v>-0.5614</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.2939</v>
+        <v>-0.2352</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.485</v>
+        <v>-0.3262</v>
       </c>
       <c r="V13" t="n">
         <v>-1.8678</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-1.2863</v>
+        <v>-0.543</v>
       </c>
       <c r="E14" t="n">
-        <v>-3.4043</v>
+        <v>-2.8197</v>
       </c>
       <c r="F14" t="n">
-        <v>2.118</v>
+        <v>2.2767</v>
       </c>
       <c r="G14" t="n">
         <v>-0.3855</v>
@@ -1546,13 +1546,13 @@
         <v>3.774</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.07049999999999999</v>
+        <v>0.6728</v>
       </c>
       <c r="T14" t="n">
-        <v>0.3338</v>
+        <v>0.9185</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.4044</v>
+        <v>-0.2457</v>
       </c>
       <c r="V14" t="n">
         <v>-0.6415999999999999</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-3.1562</v>
+        <v>-3.9827</v>
       </c>
       <c r="E15" t="n">
-        <v>-3.5964</v>
+        <v>-4.3171</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4402</v>
+        <v>0.3344</v>
       </c>
       <c r="G15" t="n">
         <v>-0.4361</v>
@@ -1624,13 +1624,13 @@
         <v>1.1322</v>
       </c>
       <c r="S15" t="n">
-        <v>1.1669</v>
+        <v>0.3404</v>
       </c>
       <c r="T15" t="n">
-        <v>1.0175</v>
+        <v>0.2968</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1494</v>
+        <v>0.0436</v>
       </c>
       <c r="V15" t="n">
         <v>-1.2452</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>30.4224</v>
+        <v>30.7161</v>
       </c>
       <c r="E16" t="n">
-        <v>24.0776</v>
+        <v>24.3716</v>
       </c>
       <c r="F16" t="n">
-        <v>6.344499999999999</v>
+        <v>6.3447</v>
       </c>
       <c r="G16" t="n">
         <v>21.76680000000001</v>
@@ -1687,7 +1687,7 @@
         <v>-9.3787</v>
       </c>
       <c r="N16" t="n">
-        <v>-9.2736</v>
+        <v>-9.273599999999998</v>
       </c>
       <c r="O16" t="n">
         <v>-0.1053000000000002</v>
@@ -1702,13 +1702,13 @@
         <v>20.757</v>
       </c>
       <c r="S16" t="n">
-        <v>5.5993</v>
+        <v>5.8932</v>
       </c>
       <c r="T16" t="n">
-        <v>5.69</v>
+        <v>5.984</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.09079999999999996</v>
+        <v>-0.09069999999999995</v>
       </c>
       <c r="V16" t="n">
         <v>1.1692</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.823</v>
+        <v>0.8146</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.0964</v>
+        <v>0.001</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9194</v>
+        <v>0.8136</v>
       </c>
       <c r="G17" t="n">
         <v>0.151</v>
@@ -1780,13 +1780,13 @@
         <v>0.5661</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1058</v>
+        <v>0.0974</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1176</v>
+        <v>-0.0201</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2234</v>
+        <v>0.1176</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.5812</v>
+        <v>-0.2095</v>
       </c>
       <c r="E19" t="n">
-        <v>1.2238</v>
+        <v>1.1264</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.805</v>
+        <v>-1.3359</v>
       </c>
       <c r="G19" t="n">
         <v>1.5256</v>
@@ -1936,13 +1936,13 @@
         <v>2.2644</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.9370000000000001</v>
+        <v>-0.5654</v>
       </c>
       <c r="T19" t="n">
-        <v>0.0152</v>
+        <v>-0.0822</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.9523</v>
+        <v>-0.4832</v>
       </c>
       <c r="V19" t="n">
         <v>-0.6036</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.6525</v>
+        <v>-0.6887</v>
       </c>
       <c r="E20" t="n">
-        <v>1.0327</v>
+        <v>0.8379</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.6853</v>
+        <v>-1.5265</v>
       </c>
       <c r="G20" t="n">
         <v>-0.9717</v>
@@ -2014,13 +2014,13 @@
         <v>0.5661</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2469</v>
+        <v>-0.283</v>
       </c>
       <c r="T20" t="n">
-        <v>0.238</v>
+        <v>0.0432</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.485</v>
+        <v>-0.3262</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>H. RIVAS OSETE</t>
+          <t>T. GOODMAN</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.2911</v>
+        <v>-1.0296</v>
       </c>
       <c r="E21" t="n">
-        <v>0.3972</v>
+        <v>2.3661</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.6882</v>
+        <v>-3.3957</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.6752</v>
+        <v>1.126</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.504</v>
+        <v>3.5115</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.1712</v>
+        <v>-2.3855</v>
       </c>
       <c r="J21" t="n">
-        <v>0.4481</v>
+        <v>5.0744</v>
       </c>
       <c r="K21" t="n">
-        <v>1.0565</v>
+        <v>5.6417</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6084000000000001</v>
+        <v>-0.5673</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.1233</v>
+        <v>-3.9484</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.5605</v>
+        <v>-2.1302</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.5628</v>
+        <v>-1.8182</v>
       </c>
       <c r="P21" t="n">
-        <v>0.5661</v>
+        <v>-1.5096</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-2.8305</v>
       </c>
       <c r="R21" t="n">
-        <v>0.5661</v>
+        <v>1.3209</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4838</v>
+        <v>-0.3442</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3527</v>
+        <v>-0.1796</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1311</v>
+        <v>-0.1646</v>
       </c>
       <c r="V21" t="n">
-        <v>0.3018</v>
+        <v>-0.3018</v>
       </c>
       <c r="W21" t="n">
         <v>0.3018</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.6036</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.509</v>
+        <v>-1.082</v>
       </c>
       <c r="E22" t="n">
-        <v>1.6257</v>
+        <v>1.5282</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.1346</v>
+        <v>-2.6103</v>
       </c>
       <c r="G22" t="n">
         <v>-1.3158</v>
@@ -2170,13 +2170,13 @@
         <v>1.6983</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.2498</v>
+        <v>-0.8228</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1328</v>
+        <v>0.0354</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.3826</v>
+        <v>-0.8582</v>
       </c>
       <c r="V22" t="n">
         <v>0.3018</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>T. GOODMAN</t>
+          <t>H. RIVAS OSETE</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.9534</v>
+        <v>-1.2466</v>
       </c>
       <c r="E23" t="n">
-        <v>1.7815</v>
+        <v>0.4946</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.7349</v>
+        <v>-1.7411</v>
       </c>
       <c r="G23" t="n">
-        <v>1.126</v>
+        <v>-1.6752</v>
       </c>
       <c r="H23" t="n">
-        <v>3.5115</v>
+        <v>-0.504</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.3855</v>
+        <v>-1.1712</v>
       </c>
       <c r="J23" t="n">
-        <v>5.0744</v>
+        <v>0.4481</v>
       </c>
       <c r="K23" t="n">
-        <v>5.6417</v>
+        <v>1.0565</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.5673</v>
+        <v>-0.6084000000000001</v>
       </c>
       <c r="M23" t="n">
-        <v>-3.9484</v>
+        <v>-2.1233</v>
       </c>
       <c r="N23" t="n">
-        <v>-2.1302</v>
+        <v>-1.5605</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.8182</v>
+        <v>-0.5628</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.5096</v>
+        <v>0.5661</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.8305</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.3209</v>
+        <v>0.5661</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.268</v>
+        <v>-0.4393</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.7642</v>
+        <v>-0.2553</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5038</v>
+        <v>-0.184</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.3018</v>
+        <v>0.3018</v>
       </c>
       <c r="W23" t="n">
         <v>0.3018</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.6036</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>T. SASTRE MIR</t>
+          <t>D. SARRIAS SANCHEZ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.4907</v>
+        <v>-3.7021</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.7936</v>
+        <v>-1.1268</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.6971</v>
+        <v>-2.5752</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.9447</v>
+        <v>-3.8094</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.3342</v>
+        <v>-2.6186</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.6106</v>
+        <v>-1.1908</v>
       </c>
       <c r="J24" t="n">
-        <v>0.2545</v>
+        <v>-0.0393</v>
       </c>
       <c r="K24" t="n">
-        <v>0.7396</v>
+        <v>-0.1472</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.485</v>
+        <v>0.1078</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.1993</v>
+        <v>-3.77</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.0737</v>
+        <v>-2.4714</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.1256</v>
+        <v>-1.2986</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.7548</v>
+        <v>-0.5661</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.8305</v>
+        <v>-3.774</v>
       </c>
       <c r="R24" t="n">
-        <v>2.0757</v>
+        <v>3.2079</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.1875</v>
+        <v>-0.27</v>
       </c>
       <c r="T24" t="n">
-        <v>0.7824</v>
+        <v>0.1961</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.9699</v>
+        <v>-0.4661</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.6036</v>
+        <v>0.9434</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>2.4904</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.6036</v>
+        <v>-1.547</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>D. SARRIAS SANCHEZ</t>
+          <t>J. CARR</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,73 +2359,73 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.6143</v>
+        <v>-3.72</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.8345</v>
+        <v>-1.8781</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.7798</v>
+        <v>-1.8419</v>
       </c>
       <c r="G25" t="n">
-        <v>-3.8094</v>
+        <v>-3.9606</v>
       </c>
       <c r="H25" t="n">
-        <v>-2.6186</v>
+        <v>-1.7546</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.1908</v>
+        <v>-2.206</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.0393</v>
+        <v>-0.3377</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.1472</v>
+        <v>0.18</v>
       </c>
       <c r="L25" t="n">
-        <v>0.1078</v>
+        <v>-0.5177</v>
       </c>
       <c r="M25" t="n">
-        <v>-3.77</v>
+        <v>-3.6229</v>
       </c>
       <c r="N25" t="n">
-        <v>-2.4714</v>
+        <v>-1.9346</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.2986</v>
+        <v>-1.6883</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.5661</v>
+        <v>-0.7548</v>
       </c>
       <c r="Q25" t="n">
-        <v>-3.774</v>
+        <v>-2.8305</v>
       </c>
       <c r="R25" t="n">
-        <v>3.2079</v>
+        <v>2.0757</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.1822</v>
+        <v>-0.2498</v>
       </c>
       <c r="T25" t="n">
-        <v>0.4884</v>
+        <v>-0.2569</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.6707</v>
+        <v>0.0071</v>
       </c>
       <c r="V25" t="n">
-        <v>0.9434</v>
+        <v>1.2452</v>
       </c>
       <c r="W25" t="n">
-        <v>2.4904</v>
+        <v>1.547</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.547</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>J. CARR</t>
+          <t>T. SASTRE MIR</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,40 +2437,40 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-4.2661</v>
+        <v>-3.8275</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.2678</v>
+        <v>-2.1834</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.9983</v>
+        <v>-1.6442</v>
       </c>
       <c r="G26" t="n">
-        <v>-3.9606</v>
+        <v>-1.9447</v>
       </c>
       <c r="H26" t="n">
-        <v>-1.7546</v>
+        <v>-0.3342</v>
       </c>
       <c r="I26" t="n">
-        <v>-2.206</v>
+        <v>-1.6106</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.3377</v>
+        <v>0.2545</v>
       </c>
       <c r="K26" t="n">
-        <v>0.18</v>
+        <v>0.7396</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.5177</v>
+        <v>-0.485</v>
       </c>
       <c r="M26" t="n">
-        <v>-3.6229</v>
+        <v>-2.1993</v>
       </c>
       <c r="N26" t="n">
-        <v>-1.9346</v>
+        <v>-1.0737</v>
       </c>
       <c r="O26" t="n">
-        <v>-1.6883</v>
+        <v>-1.1256</v>
       </c>
       <c r="P26" t="n">
         <v>-0.7548</v>
@@ -2482,22 +2482,22 @@
         <v>2.0757</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.796</v>
+        <v>-0.5244</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.6467000000000001</v>
+        <v>0.3926</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.1493</v>
+        <v>-0.917</v>
       </c>
       <c r="V26" t="n">
-        <v>1.2452</v>
+        <v>-0.6036</v>
       </c>
       <c r="W26" t="n">
-        <v>1.547</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>-0.3018</v>
+        <v>-0.6036</v>
       </c>
     </row>
     <row r="27">
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-4.5248</v>
+        <v>-4.6487</v>
       </c>
       <c r="E27" t="n">
-        <v>-3.5218</v>
+        <v>-3.6193</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.003</v>
+        <v>-1.0294</v>
       </c>
       <c r="G27" t="n">
         <v>-3.7815</v>
@@ -2560,13 +2560,13 @@
         <v>1.6983</v>
       </c>
       <c r="S27" t="n">
-        <v>-0.2528</v>
+        <v>-0.3767</v>
       </c>
       <c r="T27" t="n">
-        <v>0.1205</v>
+        <v>0.023</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.3733</v>
+        <v>-0.3997</v>
       </c>
       <c r="V27" t="n">
         <v>-0.3018</v>
@@ -2581,7 +2581,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>R. DIAZ GALIAN</t>
+          <t>H. RODRIGUEZ GUTIERREZ</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2593,73 +2593,73 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-4.9544</v>
+        <v>-4.6961</v>
       </c>
       <c r="E28" t="n">
-        <v>-3.2956</v>
+        <v>-1.1152</v>
       </c>
       <c r="F28" t="n">
-        <v>-1.6588</v>
+        <v>-3.5809</v>
       </c>
       <c r="G28" t="n">
-        <v>-5.3214</v>
+        <v>-2.4059</v>
       </c>
       <c r="H28" t="n">
-        <v>-2.2883</v>
+        <v>-0.2802</v>
       </c>
       <c r="I28" t="n">
-        <v>-3.0331</v>
+        <v>-2.1257</v>
       </c>
       <c r="J28" t="n">
-        <v>-2.4726</v>
+        <v>0.6002999999999999</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.5649999999999999</v>
+        <v>1.1676</v>
       </c>
       <c r="L28" t="n">
-        <v>-1.9076</v>
+        <v>-0.5673</v>
       </c>
       <c r="M28" t="n">
-        <v>-2.8488</v>
+        <v>-3.0062</v>
       </c>
       <c r="N28" t="n">
-        <v>-1.7233</v>
+        <v>-1.4478</v>
       </c>
       <c r="O28" t="n">
-        <v>-1.1256</v>
+        <v>-1.5584</v>
       </c>
       <c r="P28" t="n">
-        <v>0.1887</v>
+        <v>-0.1887</v>
       </c>
       <c r="Q28" t="n">
-        <v>-0.9435</v>
+        <v>-1.887</v>
       </c>
       <c r="R28" t="n">
-        <v>1.1322</v>
+        <v>1.6983</v>
       </c>
       <c r="S28" t="n">
-        <v>0.1593</v>
+        <v>0.068</v>
       </c>
       <c r="T28" t="n">
-        <v>0.1205</v>
+        <v>0.1715</v>
       </c>
       <c r="U28" t="n">
-        <v>0.0388</v>
+        <v>-0.1034</v>
       </c>
       <c r="V28" t="n">
-        <v>0.019</v>
+        <v>-2.1696</v>
       </c>
       <c r="W28" t="n">
         <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>0.019</v>
+        <v>-2.1696</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>H. RODRIGUEZ GUTIERREZ</t>
+          <t>R. DIAZ GALIAN</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2671,67 +2671,67 @@
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>-5.0246</v>
+        <v>-5.0542</v>
       </c>
       <c r="E29" t="n">
-        <v>-1.2127</v>
+        <v>-3.3931</v>
       </c>
       <c r="F29" t="n">
-        <v>-3.8119</v>
+        <v>-1.6612</v>
       </c>
       <c r="G29" t="n">
-        <v>-2.4059</v>
+        <v>-5.3214</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.2802</v>
+        <v>-2.2883</v>
       </c>
       <c r="I29" t="n">
-        <v>-2.1257</v>
+        <v>-3.0331</v>
       </c>
       <c r="J29" t="n">
-        <v>0.6002999999999999</v>
+        <v>-2.4726</v>
       </c>
       <c r="K29" t="n">
-        <v>1.1676</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="L29" t="n">
-        <v>-0.5673</v>
+        <v>-1.9076</v>
       </c>
       <c r="M29" t="n">
-        <v>-3.0062</v>
+        <v>-2.8488</v>
       </c>
       <c r="N29" t="n">
-        <v>-1.4478</v>
+        <v>-1.7233</v>
       </c>
       <c r="O29" t="n">
-        <v>-1.5584</v>
+        <v>-1.1256</v>
       </c>
       <c r="P29" t="n">
-        <v>-0.1887</v>
+        <v>0.1887</v>
       </c>
       <c r="Q29" t="n">
-        <v>-1.887</v>
+        <v>-0.9435</v>
       </c>
       <c r="R29" t="n">
-        <v>1.6983</v>
+        <v>1.1322</v>
       </c>
       <c r="S29" t="n">
-        <v>-0.2604</v>
+        <v>0.0595</v>
       </c>
       <c r="T29" t="n">
-        <v>0.074</v>
+        <v>0.023</v>
       </c>
       <c r="U29" t="n">
-        <v>-0.3344</v>
+        <v>0.0365</v>
       </c>
       <c r="V29" t="n">
-        <v>-2.1696</v>
+        <v>0.019</v>
       </c>
       <c r="W29" t="n">
         <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>-2.1696</v>
+        <v>0.019</v>
       </c>
     </row>
     <row r="30">
@@ -2749,31 +2749,31 @@
         <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>-30.4221</v>
+        <v>-28.47340000000001</v>
       </c>
       <c r="E30" t="n">
-        <v>-6.3445</v>
+        <v>-6.3447</v>
       </c>
       <c r="F30" t="n">
-        <v>-24.0775</v>
+        <v>-22.1287</v>
       </c>
       <c r="G30" t="n">
         <v>-21.7666</v>
       </c>
       <c r="H30" t="n">
-        <v>-9.751200000000001</v>
+        <v>-9.751199999999999</v>
       </c>
       <c r="I30" t="n">
         <v>-12.0155</v>
       </c>
       <c r="J30" t="n">
-        <v>9.3789</v>
+        <v>9.378900000000002</v>
       </c>
       <c r="K30" t="n">
         <v>9.273700000000002</v>
       </c>
       <c r="L30" t="n">
-        <v>0.1052000000000003</v>
+        <v>0.1051999999999995</v>
       </c>
       <c r="M30" t="n">
         <v>-31.1455</v>
@@ -2794,13 +2794,13 @@
         <v>18.87</v>
       </c>
       <c r="S30" t="n">
-        <v>-5.599299999999999</v>
+        <v>-3.6507</v>
       </c>
       <c r="T30" t="n">
-        <v>0.09059999999999994</v>
+        <v>0.09069999999999992</v>
       </c>
       <c r="U30" t="n">
-        <v>-5.6902</v>
+        <v>-3.741200000000001</v>
       </c>
       <c r="V30" t="n">
         <v>-1.1692</v>
